--- a/rpg_items.xlsx
+++ b/rpg_items.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programas\Godot\Projects\Quick-Deltarune\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuario\Documentos\Godot\Projects\Quick-Deltarune\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C8C564-EB04-4FC4-9B89-0774A5DD9490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDF86BF-61FD-410F-AA77-B15BCD39C4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t>Name</t>
   </si>
@@ -109,9 +109,6 @@
     <t xml:space="preserve">* </t>
   </si>
   <si>
-    <t>* Do 5 HP of Physical-Normal damage to 1 enemy target. Increase damage if you tap action button.</t>
-  </si>
-  <si>
     <t>* The User takes half of damage in the next turn.</t>
   </si>
   <si>
@@ -173,6 +170,172 @@
   </si>
   <si>
     <t>*Aumenta la defensa magica, inmunidad contra el Virus y Hackeado</t>
+  </si>
+  <si>
+    <t>* Do 5 of Normal-Physical Damage.</t>
+  </si>
+  <si>
+    <t>* Do 5 of Normal-Physical Damage to 1 Enemy.</t>
+  </si>
+  <si>
+    <t>* 
+* The User takes half of damage in the next turn.</t>
+  </si>
+  <si>
+    <t>max_hp</t>
+  </si>
+  <si>
+    <t>physical_attack</t>
+  </si>
+  <si>
+    <t>physical_defense</t>
+  </si>
+  <si>
+    <t>magical_attack</t>
+  </si>
+  <si>
+    <t>magical_defense</t>
+  </si>
+  <si>
+    <t>agílity</t>
+  </si>
+  <si>
+    <t>luck</t>
+  </si>
+  <si>
+    <t>physical_damage_rate</t>
+  </si>
+  <si>
+    <t>physical_presition_rate</t>
+  </si>
+  <si>
+    <t>physical_evasion_rate</t>
+  </si>
+  <si>
+    <t>magical_presition_rate</t>
+  </si>
+  <si>
+    <t>magical_evasion_rate</t>
+  </si>
+  <si>
+    <t>critical_presition_rate</t>
+  </si>
+  <si>
+    <t>critical_evasion_rate</t>
+  </si>
+  <si>
+    <t>hp_regeneration_rate</t>
+  </si>
+  <si>
+    <t>sp_regeneration_rate</t>
+  </si>
+  <si>
+    <t>tp_regeneration_rate</t>
+  </si>
+  <si>
+    <t>magical_damage_rate</t>
+  </si>
+  <si>
+    <t>gold_rate</t>
+  </si>
+  <si>
+    <t>experience_rate</t>
+  </si>
+  <si>
+    <t>guard_effect_rate</t>
+  </si>
+  <si>
+    <t>target_effect_rate</t>
+  </si>
+  <si>
+    <t>recovery_rate</t>
+  </si>
+  <si>
+    <t>pharmacólogy</t>
+  </si>
+  <si>
+    <t>Base Stats</t>
+  </si>
+  <si>
+    <t>Extra Stats</t>
+  </si>
+  <si>
+    <t>Special Stats</t>
+  </si>
+  <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>reflection_rate</t>
+  </si>
+  <si>
+    <t>affinity_rate</t>
+  </si>
+  <si>
+    <t>physical</t>
+  </si>
+  <si>
+    <t>magical</t>
+  </si>
+  <si>
+    <t>attack_rate</t>
+  </si>
+  <si>
+    <t>defense_rate</t>
+  </si>
+  <si>
+    <t>evasion_rate</t>
+  </si>
+  <si>
+    <t>critical</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>earth</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>sp</t>
+  </si>
+  <si>
+    <t>tp</t>
+  </si>
+  <si>
+    <t>cost_rate</t>
+  </si>
+  <si>
+    <t>hp_cost_rate</t>
+  </si>
+  <si>
+    <t>sp_cost_rate</t>
+  </si>
+  <si>
+    <t>tp_cost_rate</t>
+  </si>
+  <si>
+    <t>regeneration_rate</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>presition_rate</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
 </sst>
 </file>
@@ -194,12 +357,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -229,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -244,18 +413,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,33 +720,34 @@
   <dimension ref="B2:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="35.5703125" customWidth="1"/>
-    <col min="3" max="3" width="31.85546875" customWidth="1"/>
-    <col min="4" max="4" width="56.7109375" customWidth="1"/>
-    <col min="5" max="5" width="55" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="56.7109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="55" style="8" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="13" style="8" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -575,182 +756,182 @@
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+    </row>
+    <row r="5" spans="2:8" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="2:8" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
     </row>
     <row r="6" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="9" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>30</v>
+      <c r="C8" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="9"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="9"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="9"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -773,16 +954,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -806,7 +987,7 @@
       <c r="H3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1109,9 +1290,251 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE27BD71-582D-453C-BEF9-D4EE36BADC64}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:V13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="2.85546875" style="12" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="3.28515625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="2.42578125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="23" style="12" customWidth="1"/>
+    <col min="7" max="7" width="3.140625" style="12" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" style="12"/>
+    <col min="10" max="10" width="15" style="12" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="12" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="12" customWidth="1"/>
+    <col min="13" max="13" width="3" style="12" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="12" customWidth="1"/>
+    <col min="15" max="17" width="11.42578125" style="12"/>
+    <col min="18" max="18" width="2.5703125" style="12" customWidth="1"/>
+    <col min="19" max="19" width="19.28515625" style="12" customWidth="1"/>
+    <col min="20" max="16384" width="11.42578125" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B2" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="V2" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="N3" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="S3" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="N4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="S4" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="N5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="S5" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="N6" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="D11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1129,269 +1552,269 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
+        <v>35</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
-      <c r="C5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="C5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="4"/>
-      <c r="C6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
+      <c r="C6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
-      <c r="C7" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
+      <c r="C7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
       <c r="C8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
+        <v>37</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="7"/>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
+        <v>45</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="2"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
       <c r="C19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
+        <v>44</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
       <c r="F19" s="2"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="4"/>
       <c r="C20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
+        <v>38</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
       <c r="F20" s="2"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
       <c r="C21" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
       <c r="C22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
+        <v>34</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
       <c r="F22" s="2"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
       <c r="C23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="10"/>
+        <v>33</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="7"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
       <c r="F25" s="2"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
       <c r="F26" s="2"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
       <c r="F27" s="2"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
       <c r="F28" s="2"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
       <c r="F29" s="2"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
       <c r="F30" s="2"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
       <c r="F31" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
       <c r="F33" s="2"/>
     </row>
   </sheetData>
